--- a/tools/precos/planilhas/precos-oficiais-BANILA-CO.xlsx
+++ b/tools/precos/planilhas/precos-oficiais-BANILA-CO.xlsx
@@ -646,12 +646,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Clean it Zero Pore Clarifying Charcoal Capsule Clay Mask</t>
+          <t>Clean It Zero Tea-Tree EX Pore Clarifying Cleansing Balm</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" s="4" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="I3" s="4" t="n"/>
       <c r="J3" t="inlineStr">
@@ -661,7 +661,7 @@
       </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>https://banilausa.com/products/clean-it-zero-pore-clarifying-charcoal-capsule-clay-mask</t>
+          <t>https://banilausa.com/products/clean-it-zero-cleansing-balm-pore-clarifying</t>
         </is>
       </c>
       <c r="L3" s="2">
@@ -5932,7 +5932,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Site oficial: https://banilausa.com · loja "Banila Co" · moeda USD · lido em 30/10/2026 06:02 UTC</t>
+          <t>Site oficial: https://banilausa.com · loja "Banila Co" · moeda USD · lido em 30/10/2026 06:04 UTC</t>
         </is>
       </c>
     </row>

--- a/tools/precos/planilhas/precos-oficiais-BANILA-CO.xlsx
+++ b/tools/precos/planilhas/precos-oficiais-BANILA-CO.xlsx
@@ -165,8 +165,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Comparacao" displayName="Comparacao" ref="A1:N5" headerRowCount="1">
-  <autoFilter ref="A1:N5"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Comparacao" displayName="Comparacao" ref="A1:N14" headerRowCount="1">
+  <autoFilter ref="A1:N14"/>
   <tableColumns count="14">
     <tableColumn id="1" name="SKU"/>
     <tableColumn id="2" name="Nosso produto"/>
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -570,12 +570,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MB000297</t>
+          <t>MB000288</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Clean it Zero Foam Cleanser: espuma de limpeza cremosa com acerola 150 ml</t>
+          <t>Clean it Zero Brightening: bálsamo de limpeza com tangerina e vitamina C 100 ml</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>101.9</v>
+        <v>159.9</v>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
@@ -593,12 +593,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Clean it Zero Calming Foam Cleanser (150ml)</t>
+          <t>Clean it Zero Cleansing Balm Brightening</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" s="4" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="I2" s="4" t="n"/>
       <c r="J2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>https://banilausa.com/products/clean-it-zero-calming-foam-cleanser-150ml</t>
+          <t>https://banilausa.com/products/clean-it-zero-mandarin-c-cleansing-balm-brightening</t>
         </is>
       </c>
       <c r="L2" s="2">
@@ -623,12 +623,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MB000287</t>
+          <t>MB000294</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Clean it Zero Pore Clarifying: bálsamo de limpeza com melaleuca para pele oleosa 100 ml</t>
+          <t>Clean it Zero Calming: espuma de limpeza com cica para pele sensível 150 ml</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -637,21 +637,21 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>159.9</v>
-      </c>
-      <c r="E3" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>115.9</v>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Clean It Zero Tea-Tree EX Pore Clarifying Cleansing Balm</t>
+          <t>Clean it Zero Calming Foam Cleanser (150ml)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" s="4" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="I3" s="4" t="n"/>
       <c r="J3" t="inlineStr">
@@ -661,7 +661,7 @@
       </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>https://banilausa.com/products/clean-it-zero-cleansing-balm-pore-clarifying</t>
+          <t>https://banilausa.com/products/clean-it-zero-calming-foam-cleanser-150ml</t>
         </is>
       </c>
       <c r="L3" s="2">
@@ -676,12 +676,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MB003979</t>
+          <t>MB000297</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Prime Primer Finish Powder: pó finalizador matte para controle de oleosidade 12 g</t>
+          <t>Clean it Zero Foam Cleanser: espuma de limpeza cremosa com acerola 150 ml</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -690,21 +690,21 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>157.9</v>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>Conferir (tamanho/kit diferente)</t>
+        <v>101.9</v>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Prime Primer Classic – 30ML</t>
+          <t>Clean it Zero Calming Foam Cleanser (150ml)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" s="4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I4" s="4" t="n"/>
       <c r="J4" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>https://banilausa.com/products/prime-primer-classic-30ml</t>
+          <t>https://banilausa.com/products/clean-it-zero-calming-foam-cleanser-150ml</t>
         </is>
       </c>
       <c r="L4" s="2">
@@ -729,12 +729,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MB000295</t>
+          <t>MB000293</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mini Kit Clean it Zero Bálsamo (Original 7 ml + Pore Clarifying 7 ml)</t>
+          <t>Clean it Zero Nourishing: bálsamo de limpeza com ginseng para pele seca 100 ml</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -743,21 +743,21 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>999.99</v>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>Fraco — conferir</t>
+        <v>159.9</v>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Clean it Zero Tea-Tree EX Pore Clarifying Cleansing Balm Travel Kit</t>
+          <t>Clean It Zero Cleansing Balm Nourishing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" s="4" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="I5" s="4" t="n"/>
       <c r="J5" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
-          <t>https://banilausa.com/products/clean-it-zero-pore-clarifying-cleansing-balm-travel-kit</t>
+          <t>https://banilausa.com/products/clean-it-zero-cleansing-balm-nourishing</t>
         </is>
       </c>
       <c r="L5" s="2">
@@ -778,6 +778,363 @@
         <f>IF(OR(D5="",L5=""),"",D5/L5-1)</f>
         <v/>
       </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>MB000287</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Clean it Zero Pore Clarifying: bálsamo de limpeza com melaleuca para pele oleosa 100 ml</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Clean It Zero Tea-Tree EX Pore Clarifying Cleansing Balm</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="I6" s="4" t="n"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>https://banilausa.com/products/clean-it-zero-cleansing-balm-pore-clarifying</t>
+        </is>
+      </c>
+      <c r="L6" s="2">
+        <f>ROUND(H6*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M6" s="6">
+        <f>IF(OR(D6="",L6=""),"",D6/L6-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>MB003979</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Prime Primer Finish Powder: pó finalizador matte para controle de oleosidade 12 g</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>Conferir (tamanho/kit diferente)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Prime Primer Classic – 30ML</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="I7" s="4" t="n"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>https://banilausa.com/products/prime-primer-classic-30ml</t>
+        </is>
+      </c>
+      <c r="L7" s="2">
+        <f>ROUND(H7*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M7" s="6">
+        <f>IF(OR(D7="",L7=""),"",D7/L7-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>MB000296</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Dear Hydration Skin Softening Toner: tônico hidratante com cacto rosa 200 ml</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>152.9</v>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Clean it Zero Pink Hydration Toner Pads</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="I8" s="4" t="n"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>https://banilausa.com/products/clean-it-zero-pink-hydration-toner-pads</t>
+        </is>
+      </c>
+      <c r="L8" s="2">
+        <f>ROUND(H8*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M8" s="6">
+        <f>IF(OR(D8="",L8=""),"",D8/L8-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>MB000295</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Mini Kit Clean it Zero Bálsamo (Original 7 ml + Pore Clarifying 7 ml)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>999.99</v>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Clean it Zero Tea-Tree EX Pore Clarifying Cleansing Balm Travel Kit</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="I9" s="4" t="n"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>https://banilausa.com/products/clean-it-zero-pore-clarifying-cleansing-balm-travel-kit</t>
+        </is>
+      </c>
+      <c r="L9" s="2">
+        <f>ROUND(H9*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M9" s="6">
+        <f>IF(OR(D9="",L9=""),"",D9/L9-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>MB000289</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Blooming Youth Multi-Stick Balm: bálsamo em bastão com pêssego e colágeno 10,5 g</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>999.99</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="n"/>
+      <c r="I10" s="4" t="n"/>
+      <c r="L10" s="2" t="n"/>
+      <c r="M10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>MB000286</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Dear Hydration Cool Down Mist: bruma refrescante com cacto rosa 99 ml</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>115.9</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="n"/>
+      <c r="I11" s="4" t="n"/>
+      <c r="L11" s="2" t="n"/>
+      <c r="M11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>MB000290</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Dear Hydration Crystal Glow Essence: essência hidratante com cacto rosa 50 ml</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>999.99</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="n"/>
+      <c r="I12" s="4" t="n"/>
+      <c r="L12" s="2" t="n"/>
+      <c r="M12" s="6" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>MB000292</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kit Clean it Zero Pink Wonderland (4 bálsamos de 7 ml + espuma de 15 ml)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>999.99</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="n"/>
+      <c r="I13" s="4" t="n"/>
+      <c r="L13" s="2" t="n"/>
+      <c r="M13" s="6" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>MB000291</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Mini Kit Duo Dear Hydration (Creme 10 ml + Tônico 30 ml)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>999.99</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="n"/>
+      <c r="I14" s="4" t="n"/>
+      <c r="L14" s="2" t="n"/>
+      <c r="M14" s="6" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -785,10 +1142,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
   </tableParts>
 </worksheet>
 </file>
@@ -5932,7 +6293,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Site oficial: https://banilausa.com · loja "Banila Co" · moeda USD · lido em 30/10/2026 06:04 UTC</t>
+          <t>Site oficial: https://banilausa.com · loja "Banila Co" · moeda USD · lido em 30/10/2026 06:05 UTC</t>
         </is>
       </c>
     </row>

--- a/tools/precos/planilhas/precos-oficiais-BANILA-CO.xlsx
+++ b/tools/precos/planilhas/precos-oficiais-BANILA-CO.xlsx
@@ -835,12 +835,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MB003979</t>
+          <t>MB000292</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Prime Primer Finish Powder: pó finalizador matte para controle de oleosidade 12 g</t>
+          <t>Kit Clean it Zero Pink Wonderland (4 bálsamos de 7 ml + espuma de 15 ml)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -849,7 +849,7 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>157.9</v>
+        <v>999.99</v>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
@@ -858,12 +858,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Prime Primer Classic – 30ML</t>
+          <t>Clean it Zero Foam Cleanser</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" s="4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="I7" s="4" t="n"/>
       <c r="J7" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>https://banilausa.com/products/prime-primer-classic-30ml</t>
+          <t>https://banilausa.com/products/clean-it-zero-foam-cleanser</t>
         </is>
       </c>
       <c r="L7" s="2">
@@ -888,12 +888,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MB000296</t>
+          <t>MB000295</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Dear Hydration Skin Softening Toner: tônico hidratante com cacto rosa 200 ml</t>
+          <t>Mini Kit Clean it Zero Bálsamo (Original 7 ml + Pore Clarifying 7 ml)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -902,21 +902,21 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>152.9</v>
+        <v>999.99</v>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>Fraco — conferir</t>
+          <t>Conferir (tamanho/kit diferente)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Clean it Zero Pink Hydration Toner Pads</t>
+          <t>Clean It Zero Tea-Tree EX Pore Clarifying Cleansing Balm</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" s="4" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="I8" s="4" t="n"/>
       <c r="J8" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>https://banilausa.com/products/clean-it-zero-pink-hydration-toner-pads</t>
+          <t>https://banilausa.com/products/clean-it-zero-cleansing-balm-pore-clarifying</t>
         </is>
       </c>
       <c r="L8" s="2">
@@ -941,12 +941,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MB000295</t>
+          <t>MB003979</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mini Kit Clean it Zero Bálsamo (Original 7 ml + Pore Clarifying 7 ml)</t>
+          <t>Prime Primer Finish Powder: pó finalizador matte para controle de oleosidade 12 g</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -955,21 +955,21 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>999.99</v>
+        <v>157.9</v>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>Fraco — conferir</t>
+          <t>Conferir (tamanho/kit diferente)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Clean it Zero Tea-Tree EX Pore Clarifying Cleansing Balm Travel Kit</t>
+          <t>Prime Primer Classic – 30ML</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" s="4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I9" s="4" t="n"/>
       <c r="J9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>https://banilausa.com/products/clean-it-zero-pore-clarifying-cleansing-balm-travel-kit</t>
+          <t>https://banilausa.com/products/prime-primer-classic-30ml</t>
         </is>
       </c>
       <c r="L9" s="2">
@@ -994,12 +994,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MB000289</t>
+          <t>MB000296</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Blooming Youth Multi-Stick Balm: bálsamo em bastão com pêssego e colágeno 10,5 g</t>
+          <t>Dear Hydration Skin Softening Toner: tônico hidratante com cacto rosa 200 ml</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1008,27 +1008,51 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>999.99</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="n"/>
+        <v>152.9</v>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Clean it Zero Pink Hydration Toner Pads</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" s="4" t="n">
+        <v>27</v>
+      </c>
       <c r="I10" s="4" t="n"/>
-      <c r="L10" s="2" t="n"/>
-      <c r="M10" s="6" t="n"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>https://banilausa.com/products/clean-it-zero-pink-hydration-toner-pads</t>
+        </is>
+      </c>
+      <c r="L10" s="2">
+        <f>ROUND(H10*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M10" s="6">
+        <f>IF(OR(D10="",L10=""),"",D10/L10-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MB000286</t>
+          <t>MB000289</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Dear Hydration Cool Down Mist: bruma refrescante com cacto rosa 99 ml</t>
+          <t>Blooming Youth Multi-Stick Balm: bálsamo em bastão com pêssego e colágeno 10,5 g</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1037,7 +1061,7 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>115.9</v>
+        <v>999.99</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1052,12 +1076,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MB000290</t>
+          <t>MB000286</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Dear Hydration Crystal Glow Essence: essência hidratante com cacto rosa 50 ml</t>
+          <t>Dear Hydration Cool Down Mist: bruma refrescante com cacto rosa 99 ml</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1066,7 +1090,7 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>999.99</v>
+        <v>115.9</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1081,12 +1105,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MB000292</t>
+          <t>MB000290</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Kit Clean it Zero Pink Wonderland (4 bálsamos de 7 ml + espuma de 15 ml)</t>
+          <t>Dear Hydration Crystal Glow Essence: essência hidratante com cacto rosa 50 ml</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1146,10 +1170,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId10"/>
   </tableParts>
 </worksheet>
 </file>
@@ -6293,7 +6318,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Site oficial: https://banilausa.com · loja "Banila Co" · moeda USD · lido em 30/10/2026 06:05 UTC</t>
+          <t>Site oficial: https://banilausa.com · loja "Banila Co" · moeda USD · lido em 30/10/2026 06:07 UTC</t>
         </is>
       </c>
     </row>
